--- a/DEV/org.openl.rules.test/test-resources/functionality/properties_all_table_type_allowed.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/properties_all_table_type_allowed.xlsx
@@ -552,7 +552,7 @@
     <t>Increment multiplier</t>
   </si>
   <si>
-    <t>i++</t>
+    <t>i += 1</t>
   </si>
   <si>
     <t>i&lt;=Const16</t>
